--- a/thaco/design/Office-1.xlsx
+++ b/thaco/design/Office-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97CE6F5E-9CE5-414E-8EF7-B1271B95E8F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D71714EB-E57D-3C40-8F30-34699F64EFA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38560" yWindow="660" windowWidth="38080" windowHeight="20780" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/thaco/design/Office-1.xlsx
+++ b/thaco/design/Office-1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/design/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE43D57D-F56C-CC45-A709-253438FCDE92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F73AD85F-51BA-2243-A842-286B20070158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38560" yWindow="660" windowWidth="38100" windowHeight="20800" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="100" yWindow="500" windowWidth="38400" windowHeight="21100" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương CB-NV" sheetId="5" r:id="rId1"/>
@@ -8390,29 +8390,29 @@
         <v>22</v>
       </c>
       <c r="BS8" s="224"/>
-      <c r="BT8" s="226" t="s">
+      <c r="BT8" s="223" t="s">
         <v>154</v>
       </c>
-      <c r="BU8" s="240" t="s">
+      <c r="BU8" s="289" t="s">
         <v>155</v>
       </c>
       <c r="BV8" s="281"/>
-      <c r="BW8" s="252" t="s">
+      <c r="BW8" s="349" t="s">
         <v>25</v>
       </c>
-      <c r="BX8" s="245" t="s">
+      <c r="BX8" s="291" t="s">
         <v>26</v>
       </c>
-      <c r="BY8" s="246"/>
-      <c r="BZ8" s="246"/>
-      <c r="CA8" s="224"/>
-      <c r="CB8" s="225" t="s">
+      <c r="BY8" s="292"/>
+      <c r="BZ8" s="292"/>
+      <c r="CA8" s="293"/>
+      <c r="CB8" s="355" t="s">
         <v>27</v>
       </c>
-      <c r="CC8" s="218" t="s">
+      <c r="CC8" s="351" t="s">
         <v>28</v>
       </c>
-      <c r="CD8" s="218" t="s">
+      <c r="CD8" s="351" t="s">
         <v>29</v>
       </c>
       <c r="CH8" s="16"/>
@@ -8552,23 +8552,23 @@
       <c r="BO9" s="227"/>
       <c r="BP9" s="227"/>
       <c r="BQ9" s="228"/>
-      <c r="BR9" s="241" t="s">
+      <c r="BR9" s="299" t="s">
         <v>61</v>
       </c>
-      <c r="BS9" s="241" t="s">
+      <c r="BS9" s="299" t="s">
         <v>62</v>
       </c>
-      <c r="BT9" s="215"/>
-      <c r="BU9" s="221"/>
+      <c r="BT9" s="299"/>
+      <c r="BU9" s="300"/>
       <c r="BV9" s="282"/>
-      <c r="BW9" s="248"/>
-      <c r="BX9" s="221"/>
-      <c r="BY9" s="247"/>
-      <c r="BZ9" s="247"/>
-      <c r="CA9" s="248"/>
-      <c r="CB9" s="215"/>
-      <c r="CC9" s="215"/>
-      <c r="CD9" s="215"/>
+      <c r="BW9" s="350"/>
+      <c r="BX9" s="302"/>
+      <c r="BY9" s="354"/>
+      <c r="BZ9" s="354"/>
+      <c r="CA9" s="303"/>
+      <c r="CB9" s="356"/>
+      <c r="CC9" s="352"/>
+      <c r="CD9" s="352"/>
       <c r="CH9" s="16"/>
       <c r="CI9" s="17"/>
     </row>
@@ -8680,19 +8680,19 @@
       <c r="BQ10" s="226" t="s">
         <v>81</v>
       </c>
-      <c r="BR10" s="215"/>
-      <c r="BS10" s="215"/>
-      <c r="BT10" s="215"/>
-      <c r="BU10" s="221"/>
+      <c r="BR10" s="299"/>
+      <c r="BS10" s="299"/>
+      <c r="BT10" s="299"/>
+      <c r="BU10" s="300"/>
       <c r="BV10" s="282"/>
-      <c r="BW10" s="248"/>
-      <c r="BX10" s="249"/>
-      <c r="BY10" s="250"/>
-      <c r="BZ10" s="250"/>
-      <c r="CA10" s="251"/>
-      <c r="CB10" s="215"/>
-      <c r="CC10" s="215"/>
-      <c r="CD10" s="215"/>
+      <c r="BW10" s="350"/>
+      <c r="BX10" s="309"/>
+      <c r="BY10" s="310"/>
+      <c r="BZ10" s="310"/>
+      <c r="CA10" s="311"/>
+      <c r="CB10" s="356"/>
+      <c r="CC10" s="352"/>
+      <c r="CD10" s="352"/>
       <c r="CH10" s="16"/>
       <c r="CI10" s="17"/>
     </row>
@@ -8776,12 +8776,12 @@
       <c r="BO11" s="216"/>
       <c r="BP11" s="216"/>
       <c r="BQ11" s="216"/>
-      <c r="BR11" s="216"/>
-      <c r="BS11" s="216"/>
-      <c r="BT11" s="216"/>
-      <c r="BU11" s="222"/>
+      <c r="BR11" s="241"/>
+      <c r="BS11" s="241"/>
+      <c r="BT11" s="241"/>
+      <c r="BU11" s="319"/>
       <c r="BV11" s="282"/>
-      <c r="BW11" s="251"/>
+      <c r="BW11" s="301"/>
       <c r="BX11" s="61" t="s">
         <v>87</v>
       </c>
@@ -8794,9 +8794,9 @@
       <c r="CA11" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="CB11" s="219"/>
-      <c r="CC11" s="219"/>
-      <c r="CD11" s="219"/>
+      <c r="CB11" s="304"/>
+      <c r="CC11" s="305"/>
+      <c r="CD11" s="305"/>
       <c r="CE11" s="2"/>
       <c r="CF11" s="20"/>
       <c r="CH11" s="16"/>
@@ -8913,7 +8913,7 @@
         <v>0</v>
       </c>
       <c r="AH12" s="78">
-        <f t="shared" ref="AH12:AH18" si="2">CB12/26*U12</f>
+        <f>CB12/26*U12</f>
         <v>0</v>
       </c>
       <c r="AI12" s="78">
@@ -8922,12 +8922,12 @@
       </c>
       <c r="AJ12" s="78"/>
       <c r="AK12" s="78">
-        <f t="shared" ref="AK12:AK18" si="3">BZ12*L12/26</f>
+        <f>BZ12*L12/26</f>
         <v>0</v>
       </c>
       <c r="AL12" s="78"/>
       <c r="AM12" s="78">
-        <f t="shared" ref="AM12:AM18" si="4">X12*CD12</f>
+        <f>X12*CD12</f>
         <v>0</v>
       </c>
       <c r="AN12" s="78">
@@ -8935,7 +8935,7 @@
         <v>0</v>
       </c>
       <c r="AO12" s="78">
-        <f t="shared" ref="AO12:AO18" si="5">IF(F12="LN",I12*(K12+L12)/26+(H12+I12)*50%*M12/26+MAX($G12*P12/26*150%,P12*$BW12/26)-AC12+MAX($G12*Q12/26*200%,Q12*$BW12/26)-AD12+MAX($G12*R12/26*300%,R12*$BW12/26)-AE12+BW12*S12/26-AF12+AH12-AG12,I12-I12*($CF$3-K12-L12)/26+(H12+I12)*50%*M12/26+BW12*O12/26-AB12+MAX($G12*P12/26*150%,P12*$BW12/26)-AC12+MAX($G12*Q12/26*200%,Q12*$BW12/26)-AD12+MAX($G12*R12/26*300%,R12*$BW12/26)-AE12+BW12*S12/26-AF12+AH12-AG12+(G12-G12*($CF$3-K12-L12)/26-Y12)+(H12-H12*($CF$3-K12-L12)/26-AN12))</f>
+        <f>IF(F12="LN",I12*(K12+L12)/26+(H12+I12)*50%*M12/26+MAX($G12*P12/26*150%,P12*$BW12/26)-AC12+MAX($G12*Q12/26*200%,Q12*$BW12/26)-AD12+MAX($G12*R12/26*300%,R12*$BW12/26)-AE12+BW12*S12/26-AF12+AH12-AG12,I12-I12*($CF$3-K12-L12)/26+(H12+I12)*50%*M12/26+BW12*O12/26-AB12+MAX($G12*P12/26*150%,P12*$BW12/26)-AC12+MAX($G12*Q12/26*200%,Q12*$BW12/26)-AD12+MAX($G12*R12/26*300%,R12*$BW12/26)-AE12+BW12*S12/26-AF12+AH12-AG12+(G12-G12*($CF$3-K12-L12)/26-Y12)+(H12-H12*($CF$3-K12-L12)/26-AN12))</f>
         <v>50480000</v>
       </c>
       <c r="AP12" s="78"/>
@@ -8963,7 +8963,7 @@
         <v>142800</v>
       </c>
       <c r="BA12" s="72">
-        <f t="shared" ref="BA12" si="6">ROUND(IF($AX12="x",($G12+$H12)*BA$11,0),0)</f>
+        <f t="shared" ref="BA12" si="2">ROUND(IF($AX12="x",($G12+$H12)*BA$11,0),0)</f>
         <v>95200</v>
       </c>
       <c r="BB12" s="72">
@@ -8991,7 +8991,7 @@
         <v>4400000</v>
       </c>
       <c r="BJ12" s="72">
-        <f t="shared" ref="BJ12:BJ18" si="7">IF(E12="CT",11000000,0)</f>
+        <f t="shared" ref="BJ12:BJ18" si="3">IF(E12="CT",11000000,0)</f>
         <v>11000000</v>
       </c>
       <c r="BK12" s="72">
@@ -9073,7 +9073,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="78">
-        <f t="shared" ref="I13:I18" si="8">CB13-BZ13-G13-H13</f>
+        <f>CB13-BZ13-G13-H13</f>
         <v>43520000</v>
       </c>
       <c r="J13" s="79">
@@ -9124,27 +9124,27 @@
         <v>7827692.307692308</v>
       </c>
       <c r="Z13" s="78">
-        <f t="shared" ref="Z13:Z18" si="9">M13*G13/26</f>
+        <f t="shared" ref="Z13:Z18" si="4">M13*G13/26</f>
         <v>0</v>
       </c>
       <c r="AA13" s="78">
-        <f t="shared" ref="AA13:AA18" si="10">G13*N13/26</f>
+        <f t="shared" ref="AA13:AA18" si="5">G13*N13/26</f>
         <v>0</v>
       </c>
       <c r="AB13" s="78">
-        <f t="shared" ref="AB13:AB18" si="11">G13*O13/26</f>
+        <f t="shared" ref="AB13:AB18" si="6">G13*O13/26</f>
         <v>0</v>
       </c>
       <c r="AC13" s="78">
-        <f t="shared" ref="AC13:AC18" si="12">G13*P13*150%/26</f>
+        <f t="shared" ref="AC13:AC18" si="7">G13*P13*150%/26</f>
         <v>0</v>
       </c>
       <c r="AD13" s="78">
-        <f t="shared" ref="AD13:AD18" si="13">G13*Q13/26*200%</f>
+        <f t="shared" ref="AD13:AD18" si="8">G13*Q13/26*200%</f>
         <v>0</v>
       </c>
       <c r="AE13" s="78">
-        <f t="shared" ref="AE13:AE18" si="14">G13*R13/26*300%</f>
+        <f t="shared" ref="AE13:AE18" si="9">G13*R13/26*300%</f>
         <v>0</v>
       </c>
       <c r="AF13" s="78">
@@ -9152,33 +9152,33 @@
         <v>0</v>
       </c>
       <c r="AG13" s="78">
-        <f t="shared" ref="AG13:AG18" si="15">T13*G13/26/8</f>
+        <f t="shared" ref="AG13:AG18" si="10">T13*G13/26/8</f>
         <v>0</v>
       </c>
       <c r="AH13" s="78">
-        <f t="shared" si="2"/>
+        <f>CB13/26*U13</f>
         <v>0</v>
       </c>
       <c r="AI13" s="78">
-        <f t="shared" ref="AI13:AI18" si="16">G13*V13/26</f>
+        <f t="shared" ref="AI13:AI18" si="11">G13*V13/26</f>
         <v>0</v>
       </c>
       <c r="AJ13" s="78"/>
       <c r="AK13" s="78">
-        <f t="shared" si="3"/>
+        <f>BZ13*L13/26</f>
         <v>38461.538461538461</v>
       </c>
       <c r="AL13" s="78"/>
       <c r="AM13" s="78">
-        <f t="shared" si="4"/>
+        <f>X13*CD13</f>
         <v>0</v>
       </c>
       <c r="AN13" s="78">
-        <f t="shared" ref="AN13:AN18" si="17">H13/26*K13</f>
+        <f t="shared" ref="AN13:AN18" si="12">H13/26*K13</f>
         <v>0</v>
       </c>
       <c r="AO13" s="78">
-        <f t="shared" si="5"/>
+        <f>IF(F13="LN",I13*(K13+L13)/26+(H13+I13)*50%*M13/26+MAX($G13*P13/26*150%,P13*$BW13/26)-AC13+MAX($G13*Q13/26*200%,Q13*$BW13/26)-AD13+MAX($G13*R13/26*300%,R13*$BW13/26)-AE13+BW13*S13/26-AF13+AH13-AG13,I13-I13*($CF$3-K13-L13)/26+(H13+I13)*50%*M13/26+BW13*O13/26-AB13+MAX($G13*P13/26*150%,P13*$BW13/26)-AC13+MAX($G13*Q13/26*200%,Q13*$BW13/26)-AD13+MAX($G13*R13/26*300%,R13*$BW13/26)-AE13+BW13*S13/26-AF13+AH13-AG13+(G13-G13*($CF$3-K13-L13)/26-Y13)+(H13-H13*($CF$3-K13-L13)/26-AN13))</f>
         <v>40172307.692307696</v>
       </c>
       <c r="AP13" s="78"/>
@@ -9190,16 +9190,16 @@
       <c r="AT13" s="78"/>
       <c r="AU13" s="78"/>
       <c r="AV13" s="81">
-        <f t="shared" ref="AV13:AV18" si="18">Y13+Z13+AA13+AB13+AC13+AD13+AE13+AF13+AG13+AI13+AJ13+AK13+AL13+AM13+AN13+AO13+AP13-AQ13+AR13+AS13+AT13+AU13</f>
+        <f t="shared" ref="AV13:AV18" si="13">Y13+Z13+AA13+AB13+AC13+AD13+AE13+AF13+AG13+AI13+AJ13+AK13+AL13+AM13+AN13+AO13+AP13-AQ13+AR13+AS13+AT13+AU13</f>
         <v>48758461.538461544</v>
       </c>
       <c r="AW13" s="81"/>
       <c r="AX13" s="81" t="str">
-        <f t="shared" ref="AX13:AX18" si="19">IF(E13="CT","x",0)</f>
+        <f t="shared" ref="AX13:AX18" si="14">IF(E13="CT","x",0)</f>
         <v>x</v>
       </c>
       <c r="AY13" s="72">
-        <f t="shared" ref="AY13:AZ18" si="20">ROUND(IF($AX13="x",($G13+$H13)*AY$11,0),0)</f>
+        <f t="shared" ref="AY13:AZ18" si="15">ROUND(IF($AX13="x",($G13+$H13)*AY$11,0),0)</f>
         <v>678400</v>
       </c>
       <c r="AZ13" s="72">
@@ -9217,15 +9217,15 @@
       <c r="BC13" s="72"/>
       <c r="BD13" s="72"/>
       <c r="BE13" s="72">
-        <f t="shared" ref="BE13:BE18" si="21">IF(G13*1%&gt;=234000,234000,G13*1%)</f>
+        <f t="shared" ref="BE13:BE18" si="16">IF(G13*1%&gt;=234000,234000,G13*1%)</f>
         <v>84800</v>
       </c>
       <c r="BF13" s="72">
-        <f t="shared" ref="BF13:BF18" si="22">AM13+IF(E13="CT",IF(AR13&gt;=730000,730000,AR13),0)+IF(((AV13-AM13-IF(AR13&gt;=730000,730000,AR13)-AS13)*15%-AS13)&gt;"0",((AV13-AM13-IF(AR13&gt;=730000,730000,AR13)-AS13)*15%-AS13),0)</f>
+        <f t="shared" ref="BF13:BF18" si="17">AM13+IF(E13="CT",IF(AR13&gt;=730000,730000,AR13),0)+IF(((AV13-AM13-IF(AR13&gt;=730000,730000,AR13)-AS13)*15%-AS13)&gt;"0",((AV13-AM13-IF(AR13&gt;=730000,730000,AR13)-AS13)*15%-AS13),0)</f>
         <v>720000</v>
       </c>
       <c r="BG13" s="72">
-        <f t="shared" ref="BG13:BG18" si="23">AV13-BF13+AW13</f>
+        <f t="shared" ref="BG13:BG18" si="18">AV13-BF13+AW13</f>
         <v>48038461.538461544</v>
       </c>
       <c r="BH13" s="72"/>
@@ -9233,15 +9233,15 @@
         <v>4400000</v>
       </c>
       <c r="BJ13" s="72">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>11000000</v>
       </c>
       <c r="BK13" s="72">
-        <f t="shared" ref="BK13:BK18" si="24">BG13-BB13-BC13+BD13-BH13*BI13-BJ13</f>
+        <f t="shared" ref="BK13:BK18" si="19">BG13-BB13-BC13+BD13-BH13*BI13-BJ13</f>
         <v>36148061.538461544</v>
       </c>
       <c r="BL13" s="71">
-        <f t="shared" ref="BL13:BL18" si="25">IF(E13="TV",BK13*10%,IF(BK13&gt;0,ROUND(IF(BK13&gt;=80000000,BK13*35%-9850000,IF(BK13&gt;=52000000,BK13*30%-5850000,IF(BK13&gt;=32000000,BK13*25%-3250000,IF(BK13&gt;=18000000,BK13*20%-1650000,IF(BK13&gt;=10000000,BK13*15%-750000,IF(BK13&gt;5000000,BK13*10%-250000,BK13*5%)))))),0),0))</f>
+        <f t="shared" ref="BL13:BL18" si="20">IF(E13="TV",BK13*10%,IF(BK13&gt;0,ROUND(IF(BK13&gt;=80000000,BK13*35%-9850000,IF(BK13&gt;=52000000,BK13*30%-5850000,IF(BK13&gt;=32000000,BK13*25%-3250000,IF(BK13&gt;=18000000,BK13*20%-1650000,IF(BK13&gt;=10000000,BK13*15%-750000,IF(BK13&gt;5000000,BK13*10%-250000,BK13*5%)))))),0),0))</f>
         <v>5787015</v>
       </c>
       <c r="BM13" s="72"/>
@@ -9258,7 +9258,7 @@
         <v>0</v>
       </c>
       <c r="BU13" s="92">
-        <f t="shared" ref="BU13:BU18" si="26">AV13-BB13-BC13+BD13-BE13-BL13-BM13-BN13-BO13-BP13-BQ13-BR13+BS13-BT13</f>
+        <f>AV13-BB13-BC13+BD13-BE13-BL13-BM13-BN13-BO13-BP13-BQ13-BR13+BS13-BT13</f>
         <v>41996246.538461544</v>
       </c>
       <c r="BV13" s="103"/>
@@ -9275,11 +9275,11 @@
         <v>200000</v>
       </c>
       <c r="CA13" s="71">
-        <f t="shared" ref="CA13:CA18" si="27">+BW13*5%</f>
+        <f t="shared" ref="CA13:CA18" si="21">+BW13*5%</f>
         <v>2000000</v>
       </c>
       <c r="CB13" s="71">
-        <f t="shared" ref="CB13:CB18" si="28">SUM(BW13:CA13)</f>
+        <f t="shared" ref="CB13:CB18" si="22">SUM(BW13:CA13)</f>
         <v>52200000</v>
       </c>
       <c r="CC13" s="71"/>
@@ -9318,7 +9318,7 @@
         <v>0</v>
       </c>
       <c r="I14" s="78">
-        <f t="shared" si="8"/>
+        <f>CB14-BZ14-G14-H14</f>
         <v>34180000</v>
       </c>
       <c r="J14" s="79">
@@ -9369,27 +9369,27 @@
         <v>7218461.538461538</v>
       </c>
       <c r="Z14" s="78">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AA14" s="78">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AB14" s="78">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AC14" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AD14" s="78">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AE14" s="78">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AA14" s="78">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AB14" s="78">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AC14" s="78">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AD14" s="78">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AE14" s="78">
-        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AF14" s="78">
@@ -9397,33 +9397,33 @@
         <v>0</v>
       </c>
       <c r="AG14" s="78">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AH14" s="78">
-        <f t="shared" si="2"/>
+        <f>CB14/26*U14</f>
         <v>3246153.846153846</v>
       </c>
       <c r="AI14" s="78">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AJ14" s="78"/>
       <c r="AK14" s="78">
-        <f t="shared" si="3"/>
+        <f>BZ14*L14/26</f>
         <v>0</v>
       </c>
       <c r="AL14" s="78"/>
       <c r="AM14" s="78">
-        <f t="shared" si="4"/>
+        <f>X14*CD14</f>
         <v>0</v>
       </c>
       <c r="AN14" s="78">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO14" s="78">
-        <f t="shared" si="5"/>
+        <f>IF(F14="LN",I14*(K14+L14)/26+(H14+I14)*50%*M14/26+MAX($G14*P14/26*150%,P14*$BW14/26)-AC14+MAX($G14*Q14/26*200%,Q14*$BW14/26)-AD14+MAX($G14*R14/26*300%,R14*$BW14/26)-AE14+BW14*S14/26-AF14+AH14-AG14,I14-I14*($CF$3-K14-L14)/26+(H14+I14)*50%*M14/26+BW14*O14/26-AB14+MAX($G14*P14/26*150%,P14*$BW14/26)-AC14+MAX($G14*Q14/26*200%,Q14*$BW14/26)-AD14+MAX($G14*R14/26*300%,R14*$BW14/26)-AE14+BW14*S14/26-AF14+AH14-AG14+(G14-G14*($CF$3-K14-L14)/26-Y14)+(H14-H14*($CF$3-K14-L14)/26-AN14))</f>
         <v>34796923.07692308</v>
       </c>
       <c r="AP14" s="78"/>
@@ -9435,20 +9435,20 @@
       <c r="AT14" s="78"/>
       <c r="AU14" s="78"/>
       <c r="AV14" s="81">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>42575384.615384616</v>
       </c>
       <c r="AW14" s="81"/>
       <c r="AX14" s="81" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="14"/>
         <v>x</v>
       </c>
       <c r="AY14" s="72">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>625600</v>
       </c>
       <c r="AZ14" s="72">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>117300</v>
       </c>
       <c r="BA14" s="72">
@@ -9456,21 +9456,21 @@
         <v>78200</v>
       </c>
       <c r="BB14" s="72">
-        <f t="shared" ref="BB14" si="29">SUM(AY14:BA14)</f>
+        <f t="shared" ref="BB14" si="23">SUM(AY14:BA14)</f>
         <v>821100</v>
       </c>
       <c r="BC14" s="72"/>
       <c r="BD14" s="72"/>
       <c r="BE14" s="72">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>78200</v>
       </c>
       <c r="BF14" s="72">
-        <f t="shared" si="22"/>
+        <f t="shared" si="17"/>
         <v>560000</v>
       </c>
       <c r="BG14" s="72">
-        <f t="shared" si="23"/>
+        <f t="shared" si="18"/>
         <v>42015384.615384616</v>
       </c>
       <c r="BH14" s="72"/>
@@ -9478,15 +9478,15 @@
         <v>4400000</v>
       </c>
       <c r="BJ14" s="72">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>11000000</v>
       </c>
       <c r="BK14" s="72">
-        <f t="shared" si="24"/>
+        <f t="shared" si="19"/>
         <v>30194284.615384616</v>
       </c>
       <c r="BL14" s="71">
-        <f t="shared" si="25"/>
+        <f t="shared" si="20"/>
         <v>4388857</v>
       </c>
       <c r="BM14" s="72"/>
@@ -9503,7 +9503,7 @@
         <v>25846153.846153852</v>
       </c>
       <c r="BU14" s="92">
-        <f t="shared" si="26"/>
+        <f>AV14-BB14-BC14+BD14-BE14-BL14-BM14-BN14-BO14-BP14-BQ14-BR14+BS14-BT14</f>
         <v>11441073.769230764</v>
       </c>
       <c r="BV14" s="103"/>
@@ -9520,11 +9520,11 @@
         <v>200000</v>
       </c>
       <c r="CA14" s="71">
-        <f t="shared" si="27"/>
+        <f t="shared" si="21"/>
         <v>2000000</v>
       </c>
       <c r="CB14" s="71">
-        <f t="shared" si="28"/>
+        <f t="shared" si="22"/>
         <v>42200000</v>
       </c>
       <c r="CC14" s="71"/>
@@ -9563,7 +9563,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="78">
-        <f t="shared" si="8"/>
+        <f>CB15-BZ15-G15-H15</f>
         <v>19160000</v>
       </c>
       <c r="J15" s="79">
@@ -9614,27 +9614,27 @@
         <v>6990000</v>
       </c>
       <c r="Z15" s="78">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AA15" s="78">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AB15" s="78">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AC15" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AD15" s="78">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AE15" s="78">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AA15" s="78">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AB15" s="78">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AC15" s="78">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AD15" s="78">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AE15" s="78">
-        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AF15" s="78">
@@ -9642,29 +9642,29 @@
         <v>0</v>
       </c>
       <c r="AG15" s="78">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AH15" s="78">
-        <f t="shared" si="2"/>
+        <f>CB15/26*U15</f>
         <v>0</v>
       </c>
       <c r="AI15" s="78">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AJ15" s="78"/>
       <c r="AK15" s="78">
-        <f t="shared" si="3"/>
+        <f>BZ15*L15/26</f>
         <v>23076.923076923078</v>
       </c>
       <c r="AL15" s="78"/>
       <c r="AM15" s="78">
-        <f t="shared" si="4"/>
+        <f>X15*CD15</f>
         <v>0</v>
       </c>
       <c r="AN15" s="78">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO15" s="78">
@@ -9680,16 +9680,16 @@
       <c r="AT15" s="78"/>
       <c r="AU15" s="78"/>
       <c r="AV15" s="81">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>26893076.923076924</v>
       </c>
       <c r="AW15" s="81"/>
       <c r="AX15" s="81" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="14"/>
         <v>x</v>
       </c>
       <c r="AY15" s="72">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>559200</v>
       </c>
       <c r="AZ15" s="72">
@@ -9707,15 +9707,15 @@
       <c r="BC15" s="72"/>
       <c r="BD15" s="72"/>
       <c r="BE15" s="72">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>69900</v>
       </c>
       <c r="BF15" s="72">
-        <f t="shared" si="22"/>
+        <f t="shared" si="17"/>
         <v>720000</v>
       </c>
       <c r="BG15" s="72">
-        <f t="shared" si="23"/>
+        <f t="shared" si="18"/>
         <v>26173076.923076924</v>
       </c>
       <c r="BH15" s="72"/>
@@ -9723,15 +9723,15 @@
         <v>4400000</v>
       </c>
       <c r="BJ15" s="72">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>11000000</v>
       </c>
       <c r="BK15" s="72">
-        <f t="shared" si="24"/>
+        <f t="shared" si="19"/>
         <v>14439126.923076924</v>
       </c>
       <c r="BL15" s="71">
-        <f t="shared" si="25"/>
+        <f t="shared" si="20"/>
         <v>1415869</v>
       </c>
       <c r="BM15" s="72"/>
@@ -9748,7 +9748,7 @@
         <v>10195307.692307694</v>
       </c>
       <c r="BU15" s="92">
-        <f t="shared" si="26"/>
+        <f>AV15-BB15-BC15+BD15-BE15-BL15-BM15-BN15-BO15-BP15-BQ15-BR15+BS15-BT15</f>
         <v>14478050.23076923</v>
       </c>
       <c r="BV15" s="103"/>
@@ -9765,11 +9765,11 @@
         <v>200000</v>
       </c>
       <c r="CA15" s="71">
-        <f t="shared" si="27"/>
+        <f t="shared" si="21"/>
         <v>1150000</v>
       </c>
       <c r="CB15" s="71">
-        <f t="shared" si="28"/>
+        <f t="shared" si="22"/>
         <v>26350000</v>
       </c>
       <c r="CC15" s="71"/>
@@ -9808,7 +9808,7 @@
         <v>0</v>
       </c>
       <c r="I16" s="78">
-        <f t="shared" si="8"/>
+        <f>CB16-BZ16-G16-H16</f>
         <v>6700000</v>
       </c>
       <c r="J16" s="79">
@@ -9859,27 +9859,27 @@
         <v>4103846.153846154</v>
       </c>
       <c r="Z16" s="78">
+        <f t="shared" si="4"/>
+        <v>373076.92307692306</v>
+      </c>
+      <c r="AA16" s="78">
+        <f t="shared" si="5"/>
+        <v>373076.92307692306</v>
+      </c>
+      <c r="AB16" s="78">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AC16" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AD16" s="78">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AE16" s="78">
         <f t="shared" si="9"/>
-        <v>373076.92307692306</v>
-      </c>
-      <c r="AA16" s="78">
-        <f t="shared" si="10"/>
-        <v>373076.92307692306</v>
-      </c>
-      <c r="AB16" s="78">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AC16" s="78">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AD16" s="78">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AE16" s="78">
-        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AF16" s="78">
@@ -9887,29 +9887,29 @@
         <v>111923.07692307692</v>
       </c>
       <c r="AG16" s="78">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AH16" s="78">
-        <f t="shared" si="2"/>
+        <f>CB16/26*U16</f>
         <v>0</v>
       </c>
       <c r="AI16" s="78">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AJ16" s="78"/>
       <c r="AK16" s="78">
-        <f t="shared" si="3"/>
+        <f>BZ16*L16/26</f>
         <v>0</v>
       </c>
       <c r="AL16" s="78"/>
       <c r="AM16" s="78">
-        <f t="shared" si="4"/>
+        <f>X16*CD16</f>
         <v>0</v>
       </c>
       <c r="AN16" s="78">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AO16" s="78">
@@ -9925,20 +9925,20 @@
       <c r="AT16" s="78"/>
       <c r="AU16" s="78"/>
       <c r="AV16" s="81">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>12183076.923076924</v>
       </c>
       <c r="AW16" s="81"/>
       <c r="AX16" s="81" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="14"/>
         <v>x</v>
       </c>
       <c r="AY16" s="72">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>388000</v>
       </c>
       <c r="AZ16" s="72">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>72750</v>
       </c>
       <c r="BA16" s="72">
@@ -9946,21 +9946,21 @@
         <v>48500</v>
       </c>
       <c r="BB16" s="72">
-        <f t="shared" ref="BB16" si="30">SUM(AY16:BA16)</f>
+        <f t="shared" ref="BB16" si="24">SUM(AY16:BA16)</f>
         <v>509250</v>
       </c>
       <c r="BC16" s="72"/>
       <c r="BD16" s="72"/>
       <c r="BE16" s="72">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>48500</v>
       </c>
       <c r="BF16" s="72">
-        <f t="shared" si="22"/>
+        <f t="shared" si="17"/>
         <v>560000</v>
       </c>
       <c r="BG16" s="72">
-        <f t="shared" si="23"/>
+        <f t="shared" si="18"/>
         <v>11623076.923076924</v>
       </c>
       <c r="BH16" s="72"/>
@@ -9968,15 +9968,15 @@
         <v>4400000</v>
       </c>
       <c r="BJ16" s="72">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>11000000</v>
       </c>
       <c r="BK16" s="72">
-        <f t="shared" si="24"/>
+        <f t="shared" si="19"/>
         <v>113826.92307692394</v>
       </c>
       <c r="BL16" s="71">
-        <f t="shared" si="25"/>
+        <f t="shared" si="20"/>
         <v>5691</v>
       </c>
       <c r="BM16" s="72"/>
@@ -9993,7 +9993,7 @@
         <v>9977846.153846154</v>
       </c>
       <c r="BU16" s="92">
-        <f t="shared" si="26"/>
+        <f>AV16-BB16-BC16+BD16-BE16-BL16-BM16-BN16-BO16-BP16-BQ16-BR16+BS16-BT16</f>
         <v>1641789.7692307699</v>
       </c>
       <c r="BV16" s="103"/>
@@ -10010,11 +10010,11 @@
         <v>200000</v>
       </c>
       <c r="CA16" s="71">
-        <f t="shared" si="27"/>
+        <f t="shared" si="21"/>
         <v>550000</v>
       </c>
       <c r="CB16" s="71">
-        <f t="shared" si="28"/>
+        <f t="shared" si="22"/>
         <v>11750000</v>
       </c>
       <c r="CC16" s="71"/>
@@ -10053,7 +10053,7 @@
         <v>780000</v>
       </c>
       <c r="I17" s="78">
-        <f t="shared" si="8"/>
+        <f>CB17-BZ17-G17-H17</f>
         <v>17030000</v>
       </c>
       <c r="J17" s="79">
@@ -10104,27 +10104,27 @@
         <v>6340000</v>
       </c>
       <c r="Z17" s="78">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AA17" s="78">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AB17" s="78">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AC17" s="78">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="AD17" s="78">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="AE17" s="78">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AA17" s="78">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AB17" s="78">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AC17" s="78">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="AD17" s="78">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AE17" s="78">
-        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AF17" s="78">
@@ -10132,33 +10132,33 @@
         <v>0</v>
       </c>
       <c r="AG17" s="78">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AH17" s="78">
-        <f t="shared" si="2"/>
+        <f>CB17/26*U17</f>
         <v>0</v>
       </c>
       <c r="AI17" s="78">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AJ17" s="78"/>
       <c r="AK17" s="78">
-        <f t="shared" si="3"/>
+        <f>BZ17*L17/26</f>
         <v>0</v>
       </c>
       <c r="AL17" s="78"/>
       <c r="AM17" s="78">
-        <f t="shared" si="4"/>
+        <f>X17*CD17</f>
         <v>0</v>
       </c>
       <c r="AN17" s="78">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>780000</v>
       </c>
       <c r="AO17" s="78">
-        <f t="shared" si="5"/>
+        <f>IF(F17="LN",I17*(K17+L17)/26+(H17+I17)*50%*M17/26+MAX($G17*P17/26*150%,P17*$BW17/26)-AC17+MAX($G17*Q17/26*200%,Q17*$BW17/26)-AD17+MAX($G17*R17/26*300%,R17*$BW17/26)-AE17+BW17*S17/26-AF17+AH17-AG17,I17-I17*($CF$3-K17-L17)/26+(H17+I17)*50%*M17/26+BW17*O17/26-AB17+MAX($G17*P17/26*150%,P17*$BW17/26)-AC17+MAX($G17*Q17/26*200%,Q17*$BW17/26)-AD17+MAX($G17*R17/26*300%,R17*$BW17/26)-AE17+BW17*S17/26-AF17+AH17-AG17+(G17-G17*($CF$3-K17-L17)/26-Y17)+(H17-H17*($CF$3-K17-L17)/26-AN17))</f>
         <v>17030000</v>
       </c>
       <c r="AP17" s="78"/>
@@ -10170,16 +10170,16 @@
       <c r="AT17" s="78"/>
       <c r="AU17" s="78"/>
       <c r="AV17" s="81">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>24870000</v>
       </c>
       <c r="AW17" s="81"/>
       <c r="AX17" s="81">
-        <f t="shared" si="19"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AY17" s="72">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="AZ17" s="72">
@@ -10197,15 +10197,15 @@
       <c r="BC17" s="72"/>
       <c r="BD17" s="72"/>
       <c r="BE17" s="72">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>63400</v>
       </c>
       <c r="BF17" s="72">
-        <f t="shared" si="22"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="BG17" s="72">
-        <f t="shared" si="23"/>
+        <f t="shared" si="18"/>
         <v>24870000</v>
       </c>
       <c r="BH17" s="72"/>
@@ -10213,15 +10213,15 @@
         <v>4400000</v>
       </c>
       <c r="BJ17" s="72">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="BK17" s="72">
-        <f t="shared" si="24"/>
+        <f t="shared" si="19"/>
         <v>24870000</v>
       </c>
       <c r="BL17" s="71">
-        <f t="shared" si="25"/>
+        <f t="shared" si="20"/>
         <v>2487000</v>
       </c>
       <c r="BM17" s="72"/>
@@ -10238,7 +10238,7 @@
         <v>10195307.692307694</v>
       </c>
       <c r="BU17" s="92">
-        <f t="shared" si="26"/>
+        <f>AV17-BB17-BC17+BD17-BE17-BL17-BM17-BN17-BO17-BP17-BQ17-BR17+BS17-BT17</f>
         <v>12124292.307692306</v>
       </c>
       <c r="BV17" s="103"/>
@@ -10255,11 +10255,11 @@
         <v>200000</v>
       </c>
       <c r="CA17" s="71">
-        <f t="shared" si="27"/>
+        <f t="shared" si="21"/>
         <v>1150000</v>
       </c>
       <c r="CB17" s="71">
-        <f t="shared" si="28"/>
+        <f t="shared" si="22"/>
         <v>24350000</v>
       </c>
       <c r="CC17" s="71" t="s">
@@ -10300,7 +10300,7 @@
         <v>300000</v>
       </c>
       <c r="I18" s="78">
-        <f t="shared" si="8"/>
+        <f>CB18-BZ18-G18-H18</f>
         <v>11210000</v>
       </c>
       <c r="J18" s="79">
@@ -10351,27 +10351,27 @@
         <v>6340000</v>
       </c>
       <c r="Z18" s="78">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AA18" s="78">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="AB18" s="78">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="AC18" s="78">
+        <f t="shared" si="7"/>
+        <v>1828846.1538461538</v>
+      </c>
+      <c r="AD18" s="78">
+        <f t="shared" si="8"/>
+        <v>975384.61538461538</v>
+      </c>
+      <c r="AE18" s="78">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="AA18" s="78">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="AB18" s="78">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AC18" s="78">
-        <f t="shared" si="12"/>
-        <v>1828846.1538461538</v>
-      </c>
-      <c r="AD18" s="78">
-        <f t="shared" si="13"/>
-        <v>975384.61538461538</v>
-      </c>
-      <c r="AE18" s="78">
-        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AF18" s="78">
@@ -10379,33 +10379,33 @@
         <v>0</v>
       </c>
       <c r="AG18" s="78">
-        <f t="shared" si="15"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AH18" s="78">
-        <f t="shared" si="2"/>
+        <f>CB18/26*U18</f>
         <v>0</v>
       </c>
       <c r="AI18" s="78">
-        <f t="shared" si="16"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AJ18" s="78"/>
       <c r="AK18" s="78">
-        <f t="shared" si="3"/>
+        <f>BZ18*L18/26</f>
         <v>0</v>
       </c>
       <c r="AL18" s="78"/>
       <c r="AM18" s="78">
-        <f t="shared" si="4"/>
+        <f>X18*CD18</f>
         <v>0</v>
       </c>
       <c r="AN18" s="78">
-        <f t="shared" si="17"/>
+        <f t="shared" si="12"/>
         <v>300000</v>
       </c>
       <c r="AO18" s="78">
-        <f t="shared" si="5"/>
+        <f>IF(F18="LN",I18*(K18+L18)/26+(H18+I18)*50%*M18/26+MAX($G18*P18/26*150%,P18*$BW18/26)-AC18+MAX($G18*Q18/26*200%,Q18*$BW18/26)-AD18+MAX($G18*R18/26*300%,R18*$BW18/26)-AE18+BW18*S18/26-AF18+AH18-AG18,I18-I18*($CF$3-K18-L18)/26+(H18+I18)*50%*M18/26+BW18*O18/26-AB18+MAX($G18*P18/26*150%,P18*$BW18/26)-AC18+MAX($G18*Q18/26*200%,Q18*$BW18/26)-AD18+MAX($G18*R18/26*300%,R18*$BW18/26)-AE18+BW18*S18/26-AF18+AH18-AG18+(G18-G18*($CF$3-K18-L18)/26-Y18)+(H18-H18*($CF$3-K18-L18)/26-AN18))</f>
         <v>12982692.307692306</v>
       </c>
       <c r="AP18" s="78"/>
@@ -10417,20 +10417,20 @@
       <c r="AT18" s="78"/>
       <c r="AU18" s="78"/>
       <c r="AV18" s="81">
-        <f t="shared" si="18"/>
+        <f t="shared" si="13"/>
         <v>22986923.076923076</v>
       </c>
       <c r="AW18" s="81"/>
       <c r="AX18" s="81" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="14"/>
         <v>x</v>
       </c>
       <c r="AY18" s="72">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>531200</v>
       </c>
       <c r="AZ18" s="72">
-        <f t="shared" si="20"/>
+        <f t="shared" si="15"/>
         <v>99600</v>
       </c>
       <c r="BA18" s="72">
@@ -10438,21 +10438,21 @@
         <v>66400</v>
       </c>
       <c r="BB18" s="72">
-        <f t="shared" ref="BB18" si="31">SUM(AY18:BA18)</f>
+        <f t="shared" ref="BB18" si="25">SUM(AY18:BA18)</f>
         <v>697200</v>
       </c>
       <c r="BC18" s="72"/>
       <c r="BD18" s="72"/>
       <c r="BE18" s="72">
-        <f t="shared" si="21"/>
+        <f t="shared" si="16"/>
         <v>63400</v>
       </c>
       <c r="BF18" s="72">
-        <f t="shared" si="22"/>
+        <f t="shared" si="17"/>
         <v>560000</v>
       </c>
       <c r="BG18" s="72">
-        <f t="shared" si="23"/>
+        <f t="shared" si="18"/>
         <v>22426923.076923076</v>
       </c>
       <c r="BH18" s="72"/>
@@ -10460,15 +10460,15 @@
         <v>4400000</v>
       </c>
       <c r="BJ18" s="72">
-        <f t="shared" si="7"/>
+        <f t="shared" si="3"/>
         <v>11000000</v>
       </c>
       <c r="BK18" s="72">
-        <f t="shared" si="24"/>
+        <f t="shared" si="19"/>
         <v>10729723.076923076</v>
       </c>
       <c r="BL18" s="71">
-        <f t="shared" si="25"/>
+        <f t="shared" si="20"/>
         <v>859458</v>
       </c>
       <c r="BM18" s="72"/>
@@ -10485,7 +10485,7 @@
         <v>9977846.153846154</v>
       </c>
       <c r="BU18" s="92">
-        <f t="shared" si="26"/>
+        <f>AV18-BB18-BC18+BD18-BE18-BL18-BM18-BN18-BO18-BP18-BQ18-BR18+BS18-BT18</f>
         <v>11389018.923076922</v>
       </c>
       <c r="BV18" s="103"/>
@@ -10502,11 +10502,11 @@
         <v>200000</v>
       </c>
       <c r="CA18" s="71">
-        <f t="shared" si="27"/>
+        <f t="shared" si="21"/>
         <v>850000</v>
       </c>
       <c r="CB18" s="71">
-        <f t="shared" si="28"/>
+        <f t="shared" si="22"/>
         <v>18050000</v>
       </c>
       <c r="CC18" s="71" t="s">
@@ -10713,6 +10713,11 @@
   <mergeCells count="82">
     <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BQ10:BQ11"/>
+    <mergeCell ref="BW8:BW11"/>
+    <mergeCell ref="BU8:BU11"/>
+    <mergeCell ref="BT8:BT11"/>
+    <mergeCell ref="BS9:BS11"/>
+    <mergeCell ref="BR9:BR11"/>
     <mergeCell ref="BJ10:BJ11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="BL10:BL11"/>
@@ -10723,8 +10728,6 @@
     <mergeCell ref="AO9:AO11"/>
     <mergeCell ref="AY9:BL9"/>
     <mergeCell ref="BM9:BQ9"/>
-    <mergeCell ref="BR9:BR11"/>
-    <mergeCell ref="BS9:BS11"/>
     <mergeCell ref="BB10:BB11"/>
     <mergeCell ref="BC10:BC11"/>
     <mergeCell ref="BD10:BD11"/>
@@ -10760,9 +10763,6 @@
     <mergeCell ref="AX8:AX11"/>
     <mergeCell ref="AY8:BQ8"/>
     <mergeCell ref="BR8:BS8"/>
-    <mergeCell ref="BT8:BT11"/>
-    <mergeCell ref="BU8:BU11"/>
-    <mergeCell ref="BW8:BW11"/>
     <mergeCell ref="BF10:BF11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="BH10:BH11"/>
@@ -14448,24 +14448,24 @@
     <mergeCell ref="AQ5:AQ8"/>
   </mergeCells>
   <conditionalFormatting sqref="B12:B16 B1:B4 B20:B1048576 B9:BU9">
-    <cfRule type="duplicateValues" dxfId="8" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:B16 B1:B4 D10:F10 J10:BK10 BM10:BU10 B20:B1048576 BW9:CD10 B9:BU9">
-    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:C19">
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL10">
-    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:B8">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="3"/>
   </conditionalFormatting>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.21" bottom="0.17" header="0.196850393700787" footer="0.196850393700787"/>
@@ -18107,24 +18107,24 @@
     <mergeCell ref="H8:H11"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B7 B22:B1048576 B12:BU12">
-    <cfRule type="duplicateValues" dxfId="17" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B7 D13:F13 J13:BI13 BK13:CD13 B22:B1048576 B12:CD12">
-    <cfRule type="duplicateValues" dxfId="16" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:B21">
-    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="BJ13">
-    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:B11">
-    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B8:B11">
-    <cfRule type="duplicateValues" dxfId="10" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -21518,28 +21518,28 @@
     <mergeCell ref="H5:H8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B4 B12:B16 B20 B9:BU9">
-    <cfRule type="duplicateValues" dxfId="27" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B4 B12:B16 D10:F10 J10:BI10 BK10:BU10 B20 BW9:CD10 B9:BU9">
-    <cfRule type="duplicateValues" dxfId="26" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:B16 B1:B4 B20 B9:BU9">
-    <cfRule type="duplicateValues" dxfId="25" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19">
-    <cfRule type="duplicateValues" dxfId="24" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="BJ10">
-    <cfRule type="duplicateValues" dxfId="21" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:B8">
-    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:B8">
-    <cfRule type="duplicateValues" dxfId="19" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
